--- a/car_rental_workbook.xlsx
+++ b/car_rental_workbook.xlsx
@@ -11,13 +11,15 @@
     <sheet name="Read Me" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Owners" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Vehicles" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Renters" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Companies" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Rentals" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Maintenance" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Owner Payments" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Renter Receipts" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Monthly Summary" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Vehicle Loans" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Vehicle Market Values" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Renters" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Companies" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Rentals" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Maintenance" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Owner Payments" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Renter Receipts" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Monthly Summary" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="178">
   <si>
     <t xml:space="preserve">Car Rental Company Workbook</t>
   </si>
@@ -91,6 +93,18 @@
     <t xml:space="preserve">Month is stored as text like 'Oct 2026' and must match exactly across sheets.</t>
   </si>
   <si>
+    <t xml:space="preserve">Vehicle Loans and Vehicle Market Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Loans: one row per loan (amount, rate, term, start date). Installment, interest, balance and end date calculate automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle Market Values: buying price and current market value per vehicle, plus the loan, maintenance and a Suggested Daily Rate to compare with the rate you charge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The two yellow assumption cells (rental days, target return) on Vehicle Market Values drive the Suggested Daily Rate.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Owner ID</t>
   </si>
   <si>
@@ -227,6 +241,144 @@
   </si>
   <si>
     <t xml:space="preserve">Mileage columns G and H are for the same month as above; update them each month.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Interest Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term (months)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Installment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Repayment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installments Paid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installments Remaining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount Paid So Far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outstanding Balance (principal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan End Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leasing Co C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sample data. Monthly Installment = standard reducing-balance (PMT) formula. Outstanding Balance = principal still owed after the Installments Paid you type (update it each month).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes monthly payments at the same rate for the whole term. Check your bank/leasing statement for the exact balance, as fees and rate changes are not included.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year of Manufacture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buying Price (LKR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buying Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Market Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valuation Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value Lost (Depreciation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depreciation %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan Outstanding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity (Market Value - Loan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Loan Installment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Maintenance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even Daily Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Daily Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Daily Rate Charged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difference (Current - Suggested)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rate Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions (change the yellow cells)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rental days per vehicle per month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed days a vehicle is rented in a month (20 = about two-thirds of the month). Sample value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target monthly return on market value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit you want each month as a share of the vehicle's market value (1% = about 12% a year). Sample value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Break-even Daily Rate = (Monthly Loan Installment + Monthly Maintenance) / Rental days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggested Daily Rate = Break-even + (Market Value x Target return) / Rental days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buying price, market value, year and dates are sample data: use dealer quotes or recent sale listings for the real market value, and update it from time to time.</t>
   </si>
   <si>
     <t xml:space="preserve">Renter ID</t>
@@ -419,12 +571,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="dd\ mmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -506,7 +660,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -523,6 +677,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -575,7 +735,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -593,6 +753,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -656,23 +824,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -932,7 +1132,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
@@ -1048,6 +1248,29 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1066,6 +1289,431 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="str">
+        <f aca="false">Rentals!A2</f>
+        <v>RT01</v>
+      </c>
+      <c r="B2" s="9" t="str">
+        <f aca="false">Rentals!B2</f>
+        <v>V001</v>
+      </c>
+      <c r="C2" s="9" t="str">
+        <f aca="false">INDEX(Vehicles!$D$2:$D$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
+        <v>Mr. Perera</v>
+      </c>
+      <c r="D2" s="9" t="str">
+        <f aca="false">Rentals!D2</f>
+        <v>Oct 2026</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <f aca="false">Rentals!E2</f>
+        <v>10</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <f aca="false">INDEX(Vehicles!$E$2:$E$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
+        <v>6000</v>
+      </c>
+      <c r="G2" s="35" t="n">
+        <f aca="false">E2*F2</f>
+        <v>60000</v>
+      </c>
+      <c r="H2" s="35" t="n">
+        <f aca="false">IF(INDEX(Vehicles!$P$2:$P$5,MATCH(B2,Vehicles!$A$2:$A$5,0))="Owner (deducted)",SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,B2,Maintenance!$C$2:$C$200,D2),0)</f>
+        <v>2000</v>
+      </c>
+      <c r="I2" s="35" t="n">
+        <f aca="false">G2-H2</f>
+        <v>58000</v>
+      </c>
+      <c r="J2" s="10" t="n">
+        <v>58000</v>
+      </c>
+      <c r="K2" s="35" t="n">
+        <f aca="false">I2-J2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="str">
+        <f aca="false">Rentals!A3</f>
+        <v>RT02</v>
+      </c>
+      <c r="B3" s="9" t="str">
+        <f aca="false">Rentals!B3</f>
+        <v>V002</v>
+      </c>
+      <c r="C3" s="9" t="str">
+        <f aca="false">INDEX(Vehicles!$D$2:$D$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
+        <v>Mrs. Silva</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f aca="false">Rentals!D3</f>
+        <v>Oct 2026</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <f aca="false">Rentals!E3</f>
+        <v>15</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <f aca="false">INDEX(Vehicles!$E$2:$E$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
+        <v>4000</v>
+      </c>
+      <c r="G3" s="35" t="n">
+        <f aca="false">E3*F3</f>
+        <v>60000</v>
+      </c>
+      <c r="H3" s="35" t="n">
+        <f aca="false">IF(INDEX(Vehicles!$P$2:$P$5,MATCH(B3,Vehicles!$A$2:$A$5,0))="Owner (deducted)",SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,B3,Maintenance!$C$2:$C$200,D3),0)</f>
+        <v>3000</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <f aca="false">G3-H3</f>
+        <v>57000</v>
+      </c>
+      <c r="J3" s="10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="K3" s="35" t="n">
+        <f aca="false">I3-J3</f>
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="str">
+        <f aca="false">Rentals!A4</f>
+        <v>RT03</v>
+      </c>
+      <c r="B4" s="9" t="str">
+        <f aca="false">Rentals!B4</f>
+        <v>V003</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <f aca="false">INDEX(Vehicles!$D$2:$D$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
+        <v>Mr. Fernando</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f aca="false">Rentals!D4</f>
+        <v>Oct 2026</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <f aca="false">Rentals!E4</f>
+        <v>20</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <f aca="false">INDEX(Vehicles!$E$2:$E$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
+        <v>9000</v>
+      </c>
+      <c r="G4" s="35" t="n">
+        <f aca="false">E4*F4</f>
+        <v>180000</v>
+      </c>
+      <c r="H4" s="35" t="n">
+        <f aca="false">IF(INDEX(Vehicles!$P$2:$P$5,MATCH(B4,Vehicles!$A$2:$A$5,0))="Owner (deducted)",SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,B4,Maintenance!$C$2:$C$200,D4),0)</f>
+        <v>5000</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <f aca="false">G4-H4</f>
+        <v>175000</v>
+      </c>
+      <c r="J4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="35" t="n">
+        <f aca="false">I4-J4</f>
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17" t="n">
+        <f aca="false">SUM(E2:E4)</f>
+        <v>45</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="18" t="n">
+        <f aca="false">SUM(G2:G4)</f>
+        <v>300000</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <f aca="false">SUM(H2:H4)</f>
+        <v>10000</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <f aca="false">SUM(I2:I4)</f>
+        <v>290000</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <f aca="false">SUM(J2:J4)</f>
+        <v>88000</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <f aca="false">SUM(K2:K4)</f>
+        <v>202000</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="str">
+        <f aca="false">Rentals!A2</f>
+        <v>RT01</v>
+      </c>
+      <c r="B2" s="9" t="str">
+        <f aca="false">Rentals!B2</f>
+        <v>V001</v>
+      </c>
+      <c r="C2" s="9" t="str">
+        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(Rentals!C2,Renters!$A$2:$A$200,0))</f>
+        <v>Nimal</v>
+      </c>
+      <c r="D2" s="9" t="str">
+        <f aca="false">Rentals!D2</f>
+        <v>Oct 2026</v>
+      </c>
+      <c r="E2" s="9" t="n">
+        <f aca="false">Rentals!E2</f>
+        <v>10</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
+        <v>8000</v>
+      </c>
+      <c r="G2" s="35" t="n">
+        <f aca="false">E2*F2</f>
+        <v>80000</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I2" s="35" t="n">
+        <f aca="false">G2-H2</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="str">
+        <f aca="false">Rentals!A3</f>
+        <v>RT02</v>
+      </c>
+      <c r="B3" s="9" t="str">
+        <f aca="false">Rentals!B3</f>
+        <v>V002</v>
+      </c>
+      <c r="C3" s="9" t="str">
+        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(Rentals!C3,Renters!$A$2:$A$200,0))</f>
+        <v>Kamal Ltd</v>
+      </c>
+      <c r="D3" s="9" t="str">
+        <f aca="false">Rentals!D3</f>
+        <v>Oct 2026</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <f aca="false">Rentals!E3</f>
+        <v>15</v>
+      </c>
+      <c r="F3" s="14" t="n">
+        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
+        <v>5500</v>
+      </c>
+      <c r="G3" s="35" t="n">
+        <f aca="false">E3*F3</f>
+        <v>82500</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>82500</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <f aca="false">G3-H3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="str">
+        <f aca="false">Rentals!A4</f>
+        <v>RT03</v>
+      </c>
+      <c r="B4" s="9" t="str">
+        <f aca="false">Rentals!B4</f>
+        <v>V003</v>
+      </c>
+      <c r="C4" s="9" t="str">
+        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(Rentals!C4,Renters!$A$2:$A$200,0))</f>
+        <v>ABC Travels</v>
+      </c>
+      <c r="D4" s="9" t="str">
+        <f aca="false">Rentals!D4</f>
+        <v>Oct 2026</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <f aca="false">Rentals!E4</f>
+        <v>20</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
+        <v>12000</v>
+      </c>
+      <c r="G4" s="35" t="n">
+        <f aca="false">E4*F4</f>
+        <v>240000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <f aca="false">G4-H4</f>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17" t="n">
+        <f aca="false">SUM(E2:E4)</f>
+        <v>45</v>
+      </c>
+      <c r="F5" s="16"/>
+      <c r="G5" s="18" t="n">
+        <f aca="false">SUM(G2:G4)</f>
+        <v>402500</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <f aca="false">SUM(H2:H4)</f>
+        <v>232500</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <f aca="false">SUM(I2:I4)</f>
+        <v>170000</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1077,178 +1725,178 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>125</v>
+      <c r="A1" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B2" s="12" t="n">
+      <c r="A2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" s="14" t="n">
         <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$D$2:$D$200,A2)</f>
         <v>402500</v>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="14" t="n">
         <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$D$2:$D$200,A2)</f>
         <v>232500</v>
       </c>
-      <c r="D2" s="25" t="n">
+      <c r="D2" s="35" t="n">
         <f aca="false">B2-C2</f>
         <v>170000</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="14" t="n">
         <f aca="false">SUMIFS('Owner Payments'!$I$2:$I$200,'Owner Payments'!$D$2:$D$200,A2)</f>
         <v>290000</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="14" t="n">
         <f aca="false">SUMIFS('Owner Payments'!$J$2:$J$200,'Owner Payments'!$D$2:$D$200,A2)</f>
         <v>88000</v>
       </c>
-      <c r="G2" s="25" t="n">
+      <c r="G2" s="35" t="n">
         <f aca="false">E2-F2</f>
         <v>202000</v>
       </c>
-      <c r="H2" s="25" t="n">
+      <c r="H2" s="35" t="n">
         <f aca="false">B2-E2</f>
         <v>112500</v>
       </c>
-      <c r="I2" s="25" t="n">
+      <c r="I2" s="35" t="n">
         <f aca="false">C2-F2</f>
         <v>144500</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="12" t="n">
+      <c r="A3" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="14" t="n">
         <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$D$2:$D$200,A3)</f>
         <v>0</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="14" t="n">
         <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$D$2:$D$200,A3)</f>
         <v>0</v>
       </c>
-      <c r="D3" s="25" t="n">
+      <c r="D3" s="35" t="n">
         <f aca="false">B3-C3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="14" t="n">
         <f aca="false">SUMIFS('Owner Payments'!$I$2:$I$200,'Owner Payments'!$D$2:$D$200,A3)</f>
         <v>0</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="14" t="n">
         <f aca="false">SUMIFS('Owner Payments'!$J$2:$J$200,'Owner Payments'!$D$2:$D$200,A3)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="25" t="n">
+      <c r="G3" s="35" t="n">
         <f aca="false">E3-F3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="25" t="n">
+      <c r="H3" s="35" t="n">
         <f aca="false">B3-E3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="25" t="n">
+      <c r="I3" s="35" t="n">
         <f aca="false">C3-F3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="12" t="n">
+      <c r="A4" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="14" t="n">
         <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$D$2:$D$200,A4)</f>
         <v>0</v>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="14" t="n">
         <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$D$2:$D$200,A4)</f>
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="35" t="n">
         <f aca="false">B4-C4</f>
         <v>0</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="14" t="n">
         <f aca="false">SUMIFS('Owner Payments'!$I$2:$I$200,'Owner Payments'!$D$2:$D$200,A4)</f>
         <v>0</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="14" t="n">
         <f aca="false">SUMIFS('Owner Payments'!$J$2:$J$200,'Owner Payments'!$D$2:$D$200,A4)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="35" t="n">
         <f aca="false">E4-F4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="25" t="n">
+      <c r="H4" s="35" t="n">
         <f aca="false">B4-E4</f>
         <v>0</v>
       </c>
-      <c r="I4" s="25" t="n">
+      <c r="I4" s="35" t="n">
         <f aca="false">C4-F4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="16" t="n">
+      <c r="A5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="18" t="n">
         <f aca="false">SUM(B2:B4)</f>
         <v>402500</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="18" t="n">
         <f aca="false">SUM(C2:C4)</f>
         <v>232500</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="18" t="n">
         <f aca="false">SUM(D2:D4)</f>
         <v>170000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">SUM(E2:E4)</f>
         <v>290000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="18" t="n">
         <f aca="false">SUM(F2:F4)</f>
         <v>88000</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="18" t="n">
         <f aca="false">SUM(G2:G4)</f>
         <v>202000</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="18" t="n">
         <f aca="false">SUM(H2:H4)</f>
         <v>112500</v>
       </c>
-      <c r="I5" s="16" t="n">
+      <c r="I5" s="18" t="n">
         <f aca="false">SUM(I2:I4)</f>
         <v>144500</v>
       </c>
@@ -1278,59 +1926,59 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>23</v>
+      <c r="A1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>27</v>
+      <c r="A2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>31</v>
+      <c r="A3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>35</v>
+      <c r="A4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1370,296 +2018,296 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="A1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="C1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="G1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="I1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="K1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="L1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="M1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="N1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="O1" s="7" t="s">
         <v>52</v>
       </c>
+      <c r="P1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="7" t="str">
+      <c r="A2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="9" t="str">
         <f aca="false">INDEX(Owners!$B$2:$B$200,MATCH(C2,Owners!$A$2:$A$200,0))</f>
         <v>Mr. Perera</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="11" t="n">
         <v>45200</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="11" t="n">
         <v>46100</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="12" t="n">
         <f aca="false">H2-G2</f>
         <v>900</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="J2" s="12" t="n">
         <f aca="false">H2</f>
         <v>46100</v>
       </c>
-      <c r="K2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L2" s="11" t="n">
+      <c r="K2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="13" t="n">
         <v>46300</v>
       </c>
-      <c r="M2" s="9" t="n">
+      <c r="M2" s="11" t="n">
         <v>45500</v>
       </c>
-      <c r="N2" s="9" t="n">
+      <c r="N2" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="O2" s="12" t="n">
+      <c r="O2" s="14" t="n">
         <f aca="false">SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,A2,Maintenance!$C$2:$C$200,'Monthly Summary'!$A$2)</f>
         <v>2000</v>
       </c>
-      <c r="P2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q2" s="11" t="n">
+      <c r="P2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" s="13" t="n">
         <v>46392</v>
       </c>
-      <c r="R2" s="10" t="n">
+      <c r="R2" s="12" t="n">
         <f aca="false">M2+N2</f>
         <v>50500</v>
       </c>
-      <c r="S2" s="13" t="str">
+      <c r="S2" s="15" t="str">
         <f aca="false">IF(J2&gt;=R2,"SERVICE OVERDUE",IF(R2-J2&lt;=500,"Service due soon","OK"))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="7" t="str">
+      <c r="A3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="9" t="str">
         <f aca="false">INDEX(Owners!$B$2:$B$200,MATCH(C3,Owners!$A$2:$A$200,0))</f>
         <v>Mrs. Silva</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="10" t="n">
         <v>5500</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="11" t="n">
         <v>31000</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="11" t="n">
         <v>32300</v>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I3" s="12" t="n">
         <f aca="false">H3-G3</f>
         <v>1300</v>
       </c>
-      <c r="J3" s="10" t="n">
+      <c r="J3" s="12" t="n">
         <f aca="false">H3</f>
         <v>32300</v>
       </c>
-      <c r="K3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="11" t="n">
+      <c r="K3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="L3" s="13" t="n">
         <v>46307</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="11" t="n">
         <v>31600</v>
       </c>
-      <c r="N3" s="9" t="n">
+      <c r="N3" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="O3" s="12" t="n">
+      <c r="O3" s="14" t="n">
         <f aca="false">SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,A3,Maintenance!$C$2:$C$200,'Monthly Summary'!$A$2)</f>
         <v>3000</v>
       </c>
-      <c r="P3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q3" s="11" t="n">
+      <c r="P3" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q3" s="13" t="n">
         <v>46489</v>
       </c>
-      <c r="R3" s="10" t="n">
+      <c r="R3" s="12" t="n">
         <f aca="false">M3+N3</f>
         <v>41600</v>
       </c>
-      <c r="S3" s="13" t="str">
+      <c r="S3" s="15" t="str">
         <f aca="false">IF(J3&gt;=R3,"SERVICE OVERDUE",IF(R3-J3&lt;=500,"Service due soon","OK"))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="7" t="str">
+      <c r="A4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="9" t="str">
         <f aca="false">INDEX(Owners!$B$2:$B$200,MATCH(C4,Owners!$A$2:$A$200,0))</f>
         <v>Mr. Fernando</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="10" t="n">
         <v>9000</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="10" t="n">
         <v>12000</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="11" t="n">
         <v>78400</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="11" t="n">
         <v>80200</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="12" t="n">
         <f aca="false">H4-G4</f>
         <v>1800</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" s="12" t="n">
         <f aca="false">H4</f>
         <v>80200</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="11" t="n">
+      <c r="K4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="13" t="n">
         <v>46313</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="11" t="n">
         <v>79100</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="O4" s="12" t="n">
+      <c r="O4" s="14" t="n">
         <f aca="false">SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,A4,Maintenance!$C$2:$C$200,'Monthly Summary'!$A$2)</f>
         <v>5000</v>
       </c>
-      <c r="P4" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q4" s="11" t="n">
+      <c r="P4" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q4" s="13" t="n">
         <v>46495</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="R4" s="12" t="n">
         <f aca="false">M4+N4</f>
         <v>89100</v>
       </c>
-      <c r="S4" s="13" t="str">
+      <c r="S4" s="15" t="str">
         <f aca="false">IF(J4&gt;=R4,"SERVICE OVERDUE",IF(R4-J4&lt;=500,"Service due soon","OK"))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="15" t="n">
+      <c r="A6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17" t="n">
         <f aca="false">SUM(I2:I5)</f>
         <v>4000</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="16" t="n">
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="18" t="n">
         <f aca="false">SUM(O2:O5)</f>
         <v>10000</v>
       </c>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14"/>
-      <c r="R6" s="14"/>
-      <c r="S6" s="14"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>64</v>
+      <c r="A8" s="19" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>65</v>
+      <c r="A9" s="19" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1678,69 +2326,296 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="21" t="str">
+        <f aca="false">INDEX(Vehicles!$B$2:$B$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
+        <v>Toyota Axio</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F2" s="23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G2" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" s="24" t="n">
+        <v>46037</v>
+      </c>
+      <c r="I2" s="25" t="n">
+        <f aca="false">IF(F2=0,E2/G2,PMT(F2/12,G2,-E2))</f>
+        <v>66733.3430547053</v>
+      </c>
+      <c r="J2" s="25" t="n">
+        <f aca="false">I2*G2</f>
+        <v>4004000.58328232</v>
+      </c>
+      <c r="K2" s="25" t="n">
+        <f aca="false">J2-E2</f>
+        <v>1004000.58328232</v>
+      </c>
+      <c r="L2" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" s="26" t="n">
+        <f aca="false">G2-L2</f>
+        <v>50</v>
+      </c>
+      <c r="N2" s="25" t="n">
+        <f aca="false">I2*L2</f>
+        <v>667333.430547053</v>
+      </c>
+      <c r="O2" s="25" t="n">
+        <f aca="false">IF(L2&gt;=G2,0,IF(F2=0,E2-I2*L2,FV(F2/12,L2,I2,-E2)))</f>
+        <v>2615687.95761578</v>
+      </c>
+      <c r="P2" s="27" t="n">
+        <f aca="false">EDATE(H2,G2)</f>
+        <v>47863</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="21" t="str">
+        <f aca="false">INDEX(Vehicles!$B$2:$B$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
+        <v>Suzuki Wagon R</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="22" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F3" s="23" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G3" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" s="24" t="n">
+        <v>46096</v>
+      </c>
+      <c r="I3" s="25" t="n">
+        <f aca="false">IF(F3=0,E3/G3,PMT(F3/12,G3,-E3))</f>
+        <v>51691.0452229056</v>
+      </c>
+      <c r="J3" s="25" t="n">
+        <f aca="false">I3*G3</f>
+        <v>2481170.17069947</v>
+      </c>
+      <c r="K3" s="25" t="n">
+        <f aca="false">J3-E3</f>
+        <v>481170.17069947</v>
+      </c>
+      <c r="L3" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" s="26" t="n">
+        <f aca="false">G3-L3</f>
+        <v>40</v>
+      </c>
+      <c r="N3" s="25" t="n">
+        <f aca="false">I3*L3</f>
+        <v>413528.361783245</v>
+      </c>
+      <c r="O3" s="25" t="n">
+        <f aca="false">IF(L3&gt;=G3,0,IF(F3=0,E3-I3*L3,FV(F3/12,L3,I3,-E3)))</f>
+        <v>1724417.71377319</v>
+      </c>
+      <c r="P3" s="27" t="n">
+        <f aca="false">EDATE(H3,G3)</f>
+        <v>47557</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="21" t="str">
+        <f aca="false">INDEX(Vehicles!$B$2:$B$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
+        <v>Nissan Caravan</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="22" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G4" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>46188</v>
+      </c>
+      <c r="I4" s="25" t="n">
+        <f aca="false">IF(F4=0,E4/G4,PMT(F4/12,G4,-E4))</f>
+        <v>120444.631238667</v>
+      </c>
+      <c r="J4" s="25" t="n">
+        <f aca="false">I4*G4</f>
+        <v>8672013.44918406</v>
+      </c>
+      <c r="K4" s="25" t="n">
+        <f aca="false">J4-E4</f>
+        <v>2672013.44918406</v>
+      </c>
+      <c r="L4" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="26" t="n">
+        <f aca="false">G4-L4</f>
         <v>67</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>79</v>
+      <c r="N4" s="25" t="n">
+        <f aca="false">I4*L4</f>
+        <v>602223.156193337</v>
+      </c>
+      <c r="O4" s="25" t="n">
+        <f aca="false">IF(L4&gt;=G4,0,IF(F4=0,E4-I4*L4,FV(F4/12,L4,I4,-E4)))</f>
+        <v>5716704.91842534</v>
+      </c>
+      <c r="P4" s="27" t="n">
+        <f aca="false">EDATE(H4,G4)</f>
+        <v>48380</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="29" t="n">
+        <f aca="false">SUM(E2:E4)</f>
+        <v>11000000</v>
+      </c>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="29" t="n">
+        <f aca="false">SUM(I2:I4)</f>
+        <v>238869.019516278</v>
+      </c>
+      <c r="J5" s="29" t="n">
+        <f aca="false">SUM(J2:J4)</f>
+        <v>15157184.2031658</v>
+      </c>
+      <c r="K5" s="29" t="n">
+        <f aca="false">SUM(K2:K4)</f>
+        <v>4157184.20316585</v>
+      </c>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="29" t="n">
+        <f aca="false">SUM(N2:N4)</f>
+        <v>1683084.94852364</v>
+      </c>
+      <c r="O5" s="29" t="n">
+        <f aca="false">SUM(O2:O4)</f>
+        <v>10056810.5898143</v>
+      </c>
+      <c r="P5" s="28"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="30" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1759,161 +2634,370 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>88</v>
+    <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="19" t="str">
-        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(B2,Renters!$A$2:$A$200,0))</f>
-        <v>Kamal Ltd</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="18" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" s="20" t="n">
-        <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$C$2:$C$200,C2)</f>
-        <v>82500</v>
-      </c>
-      <c r="J2" s="20" t="n">
-        <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$C$2:$C$200,C2)</f>
-        <v>82500</v>
-      </c>
-      <c r="K2" s="21" t="n">
-        <f aca="false">I2-J2</f>
-        <v>0</v>
+      <c r="A2" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="21" t="str">
+        <f aca="false">INDEX(Vehicles!$B$2:$B$5,MATCH(A2,Vehicles!$A$2:$A$5,0))</f>
+        <v>Toyota Axio</v>
+      </c>
+      <c r="C2" s="20" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D2" s="22" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="E2" s="24" t="n">
+        <v>46011</v>
+      </c>
+      <c r="F2" s="22" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="G2" s="24" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H2" s="25" t="n">
+        <f aca="false">D2-F2</f>
+        <v>400000</v>
+      </c>
+      <c r="I2" s="31" t="n">
+        <f aca="false">IF(D2=0,0,H2/D2)</f>
+        <v>0.0952380952380952</v>
+      </c>
+      <c r="J2" s="32" t="n">
+        <f aca="false">SUMIFS('Vehicle Loans'!$O$2:$O$200,'Vehicle Loans'!$B$2:$B$200,A2)</f>
+        <v>2615687.95761578</v>
+      </c>
+      <c r="K2" s="25" t="n">
+        <f aca="false">F2-J2</f>
+        <v>1184312.04238422</v>
+      </c>
+      <c r="L2" s="32" t="n">
+        <f aca="false">SUMIFS('Vehicle Loans'!$I$2:$I$200,'Vehicle Loans'!$B$2:$B$200,A2)</f>
+        <v>66733.3430547053</v>
+      </c>
+      <c r="M2" s="32" t="n">
+        <f aca="false">INDEX(Vehicles!$O$2:$O$5,MATCH(A2,Vehicles!$A$2:$A$5,0))</f>
+        <v>2000</v>
+      </c>
+      <c r="N2" s="25" t="n">
+        <f aca="false">(L2+M2)/$D$10</f>
+        <v>3436.66715273527</v>
+      </c>
+      <c r="O2" s="25" t="n">
+        <f aca="false">N2+F2*$D$11/$D$10</f>
+        <v>5336.66715273527</v>
+      </c>
+      <c r="P2" s="32" t="n">
+        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(A2,Vehicles!$A$2:$A$5,0))</f>
+        <v>8000</v>
+      </c>
+      <c r="Q2" s="25" t="n">
+        <f aca="false">P2-O2</f>
+        <v>2663.33284726473</v>
+      </c>
+      <c r="R2" s="26" t="str">
+        <f aca="false">IF(P2&gt;=O2,"OK: covers cost + target",IF(P2&gt;=N2,"Covers cost, below target","BELOW BREAK-EVEN"))</f>
+        <v>OK: covers cost + target</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="19" t="str">
-        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(B3,Renters!$A$2:$A$200,0))</f>
-        <v>ABC Travels</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="H3" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="I3" s="20" t="n">
-        <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$C$2:$C$200,C3)</f>
-        <v>240000</v>
-      </c>
-      <c r="J3" s="20" t="n">
-        <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$C$2:$C$200,C3)</f>
-        <v>100000</v>
-      </c>
-      <c r="K3" s="21" t="n">
-        <f aca="false">I3-J3</f>
-        <v>140000</v>
+      <c r="A3" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="21" t="str">
+        <f aca="false">INDEX(Vehicles!$B$2:$B$5,MATCH(A3,Vehicles!$A$2:$A$5,0))</f>
+        <v>Suzuki Wagon R</v>
+      </c>
+      <c r="C3" s="20" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D3" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E3" s="24" t="n">
+        <v>46078</v>
+      </c>
+      <c r="F3" s="22" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="G3" s="24" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H3" s="25" t="n">
+        <f aca="false">D3-F3</f>
+        <v>300000</v>
+      </c>
+      <c r="I3" s="31" t="n">
+        <f aca="false">IF(D3=0,0,H3/D3)</f>
+        <v>0.1</v>
+      </c>
+      <c r="J3" s="32" t="n">
+        <f aca="false">SUMIFS('Vehicle Loans'!$O$2:$O$200,'Vehicle Loans'!$B$2:$B$200,A3)</f>
+        <v>1724417.71377319</v>
+      </c>
+      <c r="K3" s="25" t="n">
+        <f aca="false">F3-J3</f>
+        <v>975582.286226811</v>
+      </c>
+      <c r="L3" s="32" t="n">
+        <f aca="false">SUMIFS('Vehicle Loans'!$I$2:$I$200,'Vehicle Loans'!$B$2:$B$200,A3)</f>
+        <v>51691.0452229056</v>
+      </c>
+      <c r="M3" s="32" t="n">
+        <f aca="false">INDEX(Vehicles!$O$2:$O$5,MATCH(A3,Vehicles!$A$2:$A$5,0))</f>
+        <v>3000</v>
+      </c>
+      <c r="N3" s="25" t="n">
+        <f aca="false">(L3+M3)/$D$10</f>
+        <v>2734.55226114528</v>
+      </c>
+      <c r="O3" s="25" t="n">
+        <f aca="false">N3+F3*$D$11/$D$10</f>
+        <v>4084.55226114528</v>
+      </c>
+      <c r="P3" s="32" t="n">
+        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(A3,Vehicles!$A$2:$A$5,0))</f>
+        <v>5500</v>
+      </c>
+      <c r="Q3" s="25" t="n">
+        <f aca="false">P3-O3</f>
+        <v>1415.44773885472</v>
+      </c>
+      <c r="R3" s="26" t="str">
+        <f aca="false">IF(P3&gt;=O3,"OK: covers cost + target",IF(P3&gt;=N3,"Covers cost, below target","BELOW BREAK-EVEN"))</f>
+        <v>OK: covers cost + target</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="21" t="str">
+        <f aca="false">INDEX(Vehicles!$B$2:$B$5,MATCH(A4,Vehicles!$A$2:$A$5,0))</f>
+        <v>Nissan Caravan</v>
+      </c>
+      <c r="C4" s="20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D4" s="22" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>46170</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H4" s="25" t="n">
+        <f aca="false">D4-F4</f>
+        <v>900000</v>
+      </c>
+      <c r="I4" s="31" t="n">
+        <f aca="false">IF(D4=0,0,H4/D4)</f>
+        <v>0.105882352941176</v>
+      </c>
+      <c r="J4" s="32" t="n">
+        <f aca="false">SUMIFS('Vehicle Loans'!$O$2:$O$200,'Vehicle Loans'!$B$2:$B$200,A4)</f>
+        <v>5716704.91842534</v>
+      </c>
+      <c r="K4" s="25" t="n">
+        <f aca="false">F4-J4</f>
+        <v>1883295.08157466</v>
+      </c>
+      <c r="L4" s="32" t="n">
+        <f aca="false">SUMIFS('Vehicle Loans'!$I$2:$I$200,'Vehicle Loans'!$B$2:$B$200,A4)</f>
+        <v>120444.631238667</v>
+      </c>
+      <c r="M4" s="32" t="n">
+        <f aca="false">INDEX(Vehicles!$O$2:$O$5,MATCH(A4,Vehicles!$A$2:$A$5,0))</f>
+        <v>5000</v>
+      </c>
+      <c r="N4" s="25" t="n">
+        <f aca="false">(L4+M4)/$D$10</f>
+        <v>6272.23156193337</v>
+      </c>
+      <c r="O4" s="25" t="n">
+        <f aca="false">N4+F4*$D$11/$D$10</f>
+        <v>10072.2315619334</v>
+      </c>
+      <c r="P4" s="32" t="n">
+        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(A4,Vehicles!$A$2:$A$5,0))</f>
+        <v>12000</v>
+      </c>
+      <c r="Q4" s="25" t="n">
+        <f aca="false">P4-O4</f>
+        <v>1927.76843806663</v>
+      </c>
+      <c r="R4" s="26" t="str">
+        <f aca="false">IF(P4&gt;=O4,"OK: covers cost + target",IF(P4&gt;=N4,"Covers cost, below target","BELOW BREAK-EVEN"))</f>
+        <v>OK: covers cost + target</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="23" t="n">
-        <f aca="false">SUM(I2:I4)</f>
-        <v>322500</v>
-      </c>
-      <c r="J5" s="23" t="n">
+      <c r="A5" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="29" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>15700000</v>
+      </c>
+      <c r="E5" s="28"/>
+      <c r="F5" s="29" t="n">
+        <f aca="false">SUM(F2:F4)</f>
+        <v>14100000</v>
+      </c>
+      <c r="G5" s="28"/>
+      <c r="H5" s="29" t="n">
+        <f aca="false">SUM(H2:H4)</f>
+        <v>1600000</v>
+      </c>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29" t="n">
         <f aca="false">SUM(J2:J4)</f>
-        <v>182500</v>
-      </c>
-      <c r="K5" s="23" t="n">
+        <v>10056810.5898143</v>
+      </c>
+      <c r="K5" s="29" t="n">
         <f aca="false">SUM(K2:K4)</f>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>97</v>
+        <v>4043189.41018569</v>
+      </c>
+      <c r="L5" s="29" t="n">
+        <f aca="false">SUM(L2:L4)</f>
+        <v>238869.019516278</v>
+      </c>
+      <c r="M5" s="29" t="n">
+        <f aca="false">SUM(M2:M4)</f>
+        <v>10000</v>
+      </c>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1932,91 +3016,69 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>100</v>
+      <c r="A1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>10</v>
+      <c r="A2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>15</v>
+      <c r="A3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15" t="n">
-        <f aca="false">SUM(E2:E5)</f>
-        <v>45</v>
+      <c r="A4" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2035,92 +3097,161 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>107</v>
+    <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>2000</v>
+      <c r="A2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="9" t="str">
+        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(B2,Renters!$A$2:$A$200,0))</f>
+        <v>Kamal Ltd</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" s="14" t="n">
+        <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$C$2:$C$200,C2)</f>
+        <v>82500</v>
+      </c>
+      <c r="J2" s="14" t="n">
+        <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$C$2:$C$200,C2)</f>
+        <v>82500</v>
+      </c>
+      <c r="K2" s="35" t="n">
+        <f aca="false">I2-J2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="16" t="n">
-        <f aca="false">SUM(E2:E5)</f>
-        <v>10000</v>
+      <c r="A3" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" s="9" t="str">
+        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(B3,Renters!$A$2:$A$200,0))</f>
+        <v>ABC Travels</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <f aca="false">SUMIFS('Renter Receipts'!$G$2:$G$200,'Renter Receipts'!$C$2:$C$200,C3)</f>
+        <v>240000</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <f aca="false">SUMIFS('Renter Receipts'!$H$2:$H$200,'Renter Receipts'!$C$2:$C$200,C3)</f>
+        <v>100000</v>
+      </c>
+      <c r="K3" s="35" t="n">
+        <f aca="false">I3-J3</f>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="18" t="n">
+        <f aca="false">SUM(I2:I4)</f>
+        <v>322500</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <f aca="false">SUM(J2:J4)</f>
+        <v>182500</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <f aca="false">SUM(K2:K4)</f>
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -2139,220 +3270,91 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="A1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>117</v>
+      <c r="D1" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="str">
-        <f aca="false">Rentals!A2</f>
-        <v>RT01</v>
-      </c>
-      <c r="B2" s="7" t="str">
-        <f aca="false">Rentals!B2</f>
-        <v>V001</v>
-      </c>
-      <c r="C2" s="7" t="str">
-        <f aca="false">INDEX(Vehicles!$D$2:$D$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
-        <v>Mr. Perera</v>
-      </c>
-      <c r="D2" s="7" t="str">
-        <f aca="false">Rentals!D2</f>
-        <v>Oct 2026</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <f aca="false">Rentals!E2</f>
+      <c r="A2" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F2" s="12" t="n">
-        <f aca="false">INDEX(Vehicles!$E$2:$E$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
-        <v>6000</v>
-      </c>
-      <c r="G2" s="25" t="n">
-        <f aca="false">E2*F2</f>
-        <v>60000</v>
-      </c>
-      <c r="H2" s="25" t="n">
-        <f aca="false">IF(INDEX(Vehicles!$P$2:$P$5,MATCH(B2,Vehicles!$A$2:$A$5,0))="Owner (deducted)",SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,B2,Maintenance!$C$2:$C$200,D2),0)</f>
-        <v>2000</v>
-      </c>
-      <c r="I2" s="25" t="n">
-        <f aca="false">G2-H2</f>
-        <v>58000</v>
-      </c>
-      <c r="J2" s="8" t="n">
-        <v>58000</v>
-      </c>
-      <c r="K2" s="25" t="n">
-        <f aca="false">I2-J2</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="str">
-        <f aca="false">Rentals!A3</f>
-        <v>RT02</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <f aca="false">Rentals!B3</f>
-        <v>V002</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <f aca="false">INDEX(Vehicles!$D$2:$D$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
-        <v>Mrs. Silva</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <f aca="false">Rentals!D3</f>
-        <v>Oct 2026</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <f aca="false">Rentals!E3</f>
+      <c r="A3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F3" s="12" t="n">
-        <f aca="false">INDEX(Vehicles!$E$2:$E$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
-        <v>4000</v>
-      </c>
-      <c r="G3" s="25" t="n">
-        <f aca="false">E3*F3</f>
-        <v>60000</v>
-      </c>
-      <c r="H3" s="25" t="n">
-        <f aca="false">IF(INDEX(Vehicles!$P$2:$P$5,MATCH(B3,Vehicles!$A$2:$A$5,0))="Owner (deducted)",SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,B3,Maintenance!$C$2:$C$200,D3),0)</f>
-        <v>3000</v>
-      </c>
-      <c r="I3" s="25" t="n">
-        <f aca="false">G3-H3</f>
-        <v>57000</v>
-      </c>
-      <c r="J3" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="K3" s="25" t="n">
-        <f aca="false">I3-J3</f>
-        <v>27000</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="str">
-        <f aca="false">Rentals!A4</f>
-        <v>RT03</v>
-      </c>
-      <c r="B4" s="7" t="str">
-        <f aca="false">Rentals!B4</f>
-        <v>V003</v>
-      </c>
-      <c r="C4" s="7" t="str">
-        <f aca="false">INDEX(Vehicles!$D$2:$D$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
-        <v>Mr. Fernando</v>
-      </c>
-      <c r="D4" s="7" t="str">
-        <f aca="false">Rentals!D4</f>
-        <v>Oct 2026</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <f aca="false">Rentals!E4</f>
+      <c r="A4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="12" t="n">
-        <f aca="false">INDEX(Vehicles!$E$2:$E$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
-        <v>9000</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <f aca="false">E4*F4</f>
-        <v>180000</v>
-      </c>
-      <c r="H4" s="25" t="n">
-        <f aca="false">IF(INDEX(Vehicles!$P$2:$P$5,MATCH(B4,Vehicles!$A$2:$A$5,0))="Owner (deducted)",SUMIFS(Maintenance!$E$2:$E$200,Maintenance!$B$2:$B$200,B4,Maintenance!$C$2:$C$200,D4),0)</f>
-        <v>5000</v>
-      </c>
-      <c r="I4" s="25" t="n">
-        <f aca="false">G4-H4</f>
-        <v>175000</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="25" t="n">
-        <f aca="false">I4-J4</f>
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15" t="n">
-        <f aca="false">SUM(E2:E4)</f>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="17" t="n">
+        <f aca="false">SUM(E2:E5)</f>
         <v>45</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="16" t="n">
-        <f aca="false">SUM(G2:G4)</f>
-        <v>300000</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <f aca="false">SUM(H2:H4)</f>
-        <v>10000</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <f aca="false">SUM(I2:I4)</f>
-        <v>290000</v>
-      </c>
-      <c r="J5" s="16" t="n">
-        <f aca="false">SUM(J2:J4)</f>
-        <v>88000</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <f aca="false">SUM(K2:K4)</f>
-        <v>202000</v>
       </c>
     </row>
   </sheetData>
@@ -2371,181 +3373,92 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>88</v>
+      <c r="A1" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="str">
-        <f aca="false">Rentals!A2</f>
-        <v>RT01</v>
-      </c>
-      <c r="B2" s="7" t="str">
-        <f aca="false">Rentals!B2</f>
-        <v>V001</v>
-      </c>
-      <c r="C2" s="7" t="str">
-        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(Rentals!C2,Renters!$A$2:$A$200,0))</f>
-        <v>Nimal</v>
-      </c>
-      <c r="D2" s="7" t="str">
-        <f aca="false">Rentals!D2</f>
-        <v>Oct 2026</v>
-      </c>
-      <c r="E2" s="7" t="n">
-        <f aca="false">Rentals!E2</f>
-        <v>10</v>
-      </c>
-      <c r="F2" s="12" t="n">
-        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(B2,Vehicles!$A$2:$A$5,0))</f>
-        <v>8000</v>
-      </c>
-      <c r="G2" s="25" t="n">
-        <f aca="false">E2*F2</f>
-        <v>80000</v>
-      </c>
-      <c r="H2" s="8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="I2" s="25" t="n">
-        <f aca="false">G2-H2</f>
-        <v>30000</v>
+      <c r="A2" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="str">
-        <f aca="false">Rentals!A3</f>
-        <v>RT02</v>
-      </c>
-      <c r="B3" s="7" t="str">
-        <f aca="false">Rentals!B3</f>
-        <v>V002</v>
-      </c>
-      <c r="C3" s="7" t="str">
-        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(Rentals!C3,Renters!$A$2:$A$200,0))</f>
-        <v>Kamal Ltd</v>
-      </c>
-      <c r="D3" s="7" t="str">
-        <f aca="false">Rentals!D3</f>
-        <v>Oct 2026</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <f aca="false">Rentals!E3</f>
-        <v>15</v>
-      </c>
-      <c r="F3" s="12" t="n">
-        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(B3,Vehicles!$A$2:$A$5,0))</f>
-        <v>5500</v>
-      </c>
-      <c r="G3" s="25" t="n">
-        <f aca="false">E3*F3</f>
-        <v>82500</v>
-      </c>
-      <c r="H3" s="8" t="n">
-        <v>82500</v>
-      </c>
-      <c r="I3" s="25" t="n">
-        <f aca="false">G3-H3</f>
-        <v>0</v>
+      <c r="A3" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="str">
-        <f aca="false">Rentals!A4</f>
-        <v>RT03</v>
-      </c>
-      <c r="B4" s="7" t="str">
-        <f aca="false">Rentals!B4</f>
-        <v>V003</v>
-      </c>
-      <c r="C4" s="7" t="str">
-        <f aca="false">INDEX(Renters!$B$2:$B$200,MATCH(Rentals!C4,Renters!$A$2:$A$200,0))</f>
-        <v>ABC Travels</v>
-      </c>
-      <c r="D4" s="7" t="str">
-        <f aca="false">Rentals!D4</f>
-        <v>Oct 2026</v>
-      </c>
-      <c r="E4" s="7" t="n">
-        <f aca="false">Rentals!E4</f>
-        <v>20</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <f aca="false">INDEX(Vehicles!$F$2:$F$5,MATCH(B4,Vehicles!$A$2:$A$5,0))</f>
-        <v>12000</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <f aca="false">E4*F4</f>
-        <v>240000</v>
-      </c>
-      <c r="H4" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="I4" s="25" t="n">
-        <f aca="false">G4-H4</f>
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="15" t="n">
-        <f aca="false">SUM(E2:E4)</f>
-        <v>45</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="16" t="n">
-        <f aca="false">SUM(G2:G4)</f>
-        <v>402500</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <f aca="false">SUM(H2:H4)</f>
-        <v>232500</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <f aca="false">SUM(I2:I4)</f>
-        <v>170000</v>
+      <c r="A4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="18" t="n">
+        <f aca="false">SUM(E2:E5)</f>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
